--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI54"/>
+  <dimension ref="A1:BI55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -11354,6 +11354,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>20260914</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>25</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-T酒仙,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>24</v>
+      </c>
+      <c r="J55" t="n">
+        <v>25</v>
+      </c>
+      <c r="K55" t="n">
+        <v>24</v>
+      </c>
+      <c r="L55" t="n">
+        <v>25</v>
+      </c>
+      <c r="M55" t="n">
+        <v>25</v>
+      </c>
+      <c r="N55" t="n">
+        <v>24</v>
+      </c>
+      <c r="O55" t="n">
+        <v>25</v>
+      </c>
+      <c r="P55" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R55" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V55" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W55" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X55" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>4042.42</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>4271.04</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI55"/>
+  <dimension ref="A1:BI56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -11543,6 +11543,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>20260915</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>25</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>24</v>
+      </c>
+      <c r="J56" t="n">
+        <v>25</v>
+      </c>
+      <c r="K56" t="n">
+        <v>24</v>
+      </c>
+      <c r="L56" t="n">
+        <v>25</v>
+      </c>
+      <c r="M56" t="n">
+        <v>25</v>
+      </c>
+      <c r="N56" t="n">
+        <v>24</v>
+      </c>
+      <c r="O56" t="n">
+        <v>25</v>
+      </c>
+      <c r="P56" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R56" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V56" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W56" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X56" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>4042.41</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>4271.04</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI56"/>
+  <dimension ref="A1:BI57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -11732,6 +11732,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>20260916</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>25</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>24</v>
+      </c>
+      <c r="J57" t="n">
+        <v>25</v>
+      </c>
+      <c r="K57" t="n">
+        <v>24</v>
+      </c>
+      <c r="L57" t="n">
+        <v>25</v>
+      </c>
+      <c r="M57" t="n">
+        <v>25</v>
+      </c>
+      <c r="N57" t="n">
+        <v>24</v>
+      </c>
+      <c r="O57" t="n">
+        <v>25</v>
+      </c>
+      <c r="P57" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R57" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S57" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V57" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W57" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X57" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>4042.41</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>4270.99</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI57"/>
+  <dimension ref="A1:BI58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -11921,6 +11921,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>20260917</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>26</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>24</v>
+      </c>
+      <c r="J58" t="n">
+        <v>25</v>
+      </c>
+      <c r="K58" t="n">
+        <v>24</v>
+      </c>
+      <c r="L58" t="n">
+        <v>25</v>
+      </c>
+      <c r="M58" t="n">
+        <v>25</v>
+      </c>
+      <c r="N58" t="n">
+        <v>24</v>
+      </c>
+      <c r="O58" t="n">
+        <v>25</v>
+      </c>
+      <c r="P58" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R58" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V58" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W58" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X58" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>4042.4</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>4270.99</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI58"/>
+  <dimension ref="A1:BI59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -12110,6 +12110,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>26</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>24</v>
+      </c>
+      <c r="J59" t="n">
+        <v>25</v>
+      </c>
+      <c r="K59" t="n">
+        <v>24</v>
+      </c>
+      <c r="L59" t="n">
+        <v>25</v>
+      </c>
+      <c r="M59" t="n">
+        <v>25</v>
+      </c>
+      <c r="N59" t="n">
+        <v>24</v>
+      </c>
+      <c r="O59" t="n">
+        <v>25</v>
+      </c>
+      <c r="P59" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R59" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V59" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W59" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X59" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>4340.5</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>4042.38</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>4270.94</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI59"/>
+  <dimension ref="A1:BI60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -12299,6 +12299,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>20260919</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>26</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G60" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>24</v>
+      </c>
+      <c r="J60" t="n">
+        <v>25</v>
+      </c>
+      <c r="K60" t="n">
+        <v>24</v>
+      </c>
+      <c r="L60" t="n">
+        <v>25</v>
+      </c>
+      <c r="M60" t="n">
+        <v>25</v>
+      </c>
+      <c r="N60" t="n">
+        <v>24</v>
+      </c>
+      <c r="O60" t="n">
+        <v>25</v>
+      </c>
+      <c r="P60" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R60" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S60" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V60" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W60" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X60" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>4042.34</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>4270.94</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI60"/>
+  <dimension ref="A1:BI61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -12488,6 +12488,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>20260920</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>26</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>24</v>
+      </c>
+      <c r="J61" t="n">
+        <v>25</v>
+      </c>
+      <c r="K61" t="n">
+        <v>24</v>
+      </c>
+      <c r="L61" t="n">
+        <v>25</v>
+      </c>
+      <c r="M61" t="n">
+        <v>25</v>
+      </c>
+      <c r="N61" t="n">
+        <v>24</v>
+      </c>
+      <c r="O61" t="n">
+        <v>25</v>
+      </c>
+      <c r="P61" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R61" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V61" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W61" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X61" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>4042.32</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>4270.94</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI61"/>
+  <dimension ref="A1:BI62"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -12677,6 +12677,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>20260921</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>26</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F62" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>24</v>
+      </c>
+      <c r="J62" t="n">
+        <v>25</v>
+      </c>
+      <c r="K62" t="n">
+        <v>24</v>
+      </c>
+      <c r="L62" t="n">
+        <v>25</v>
+      </c>
+      <c r="M62" t="n">
+        <v>25</v>
+      </c>
+      <c r="N62" t="n">
+        <v>24</v>
+      </c>
+      <c r="O62" t="n">
+        <v>25</v>
+      </c>
+      <c r="P62" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R62" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S62" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V62" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W62" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X62" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>4042.32</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI62" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI62"/>
+  <dimension ref="A1:BI63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -12866,6 +12866,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>20260922</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>26</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>24</v>
+      </c>
+      <c r="J63" t="n">
+        <v>25</v>
+      </c>
+      <c r="K63" t="n">
+        <v>24</v>
+      </c>
+      <c r="L63" t="n">
+        <v>25</v>
+      </c>
+      <c r="M63" t="n">
+        <v>25</v>
+      </c>
+      <c r="N63" t="n">
+        <v>24</v>
+      </c>
+      <c r="O63" t="n">
+        <v>25</v>
+      </c>
+      <c r="P63" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R63" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V63" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W63" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X63" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>4042.31</v>
+      </c>
+      <c r="BF63" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI63" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI63"/>
+  <dimension ref="A1:BI64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -13055,6 +13055,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>20260923</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>26</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>24</v>
+      </c>
+      <c r="J64" t="n">
+        <v>25</v>
+      </c>
+      <c r="K64" t="n">
+        <v>24</v>
+      </c>
+      <c r="L64" t="n">
+        <v>25</v>
+      </c>
+      <c r="M64" t="n">
+        <v>25</v>
+      </c>
+      <c r="N64" t="n">
+        <v>24</v>
+      </c>
+      <c r="O64" t="n">
+        <v>25</v>
+      </c>
+      <c r="P64" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R64" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V64" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W64" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X64" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>4042.31</v>
+      </c>
+      <c r="BF64" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI64" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI64"/>
+  <dimension ref="A1:BI65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -13244,6 +13244,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>20260924</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>27</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>24</v>
+      </c>
+      <c r="J65" t="n">
+        <v>25</v>
+      </c>
+      <c r="K65" t="n">
+        <v>24</v>
+      </c>
+      <c r="L65" t="n">
+        <v>25</v>
+      </c>
+      <c r="M65" t="n">
+        <v>25</v>
+      </c>
+      <c r="N65" t="n">
+        <v>24</v>
+      </c>
+      <c r="O65" t="n">
+        <v>25</v>
+      </c>
+      <c r="P65" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R65" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V65" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W65" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X65" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>4042.31</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI65" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI65"/>
+  <dimension ref="A1:BI66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -13433,6 +13433,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>20260925</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>27</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>24</v>
+      </c>
+      <c r="J66" t="n">
+        <v>25</v>
+      </c>
+      <c r="K66" t="n">
+        <v>24</v>
+      </c>
+      <c r="L66" t="n">
+        <v>25</v>
+      </c>
+      <c r="M66" t="n">
+        <v>25</v>
+      </c>
+      <c r="N66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O66" t="n">
+        <v>25</v>
+      </c>
+      <c r="P66" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R66" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V66" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W66" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X66" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>4042.3</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI66"/>
+  <dimension ref="A1:BI67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -13622,6 +13622,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>20260926</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>27</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>24</v>
+      </c>
+      <c r="J67" t="n">
+        <v>25</v>
+      </c>
+      <c r="K67" t="n">
+        <v>24</v>
+      </c>
+      <c r="L67" t="n">
+        <v>25</v>
+      </c>
+      <c r="M67" t="n">
+        <v>25</v>
+      </c>
+      <c r="N67" t="n">
+        <v>24</v>
+      </c>
+      <c r="O67" t="n">
+        <v>25</v>
+      </c>
+      <c r="P67" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R67" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V67" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W67" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X67" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>4042.29</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI67"/>
+  <dimension ref="A1:BI68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -13811,6 +13811,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>20260927</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>27</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G68" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Speedk-D冰DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>24</v>
+      </c>
+      <c r="J68" t="n">
+        <v>25</v>
+      </c>
+      <c r="K68" t="n">
+        <v>24</v>
+      </c>
+      <c r="L68" t="n">
+        <v>25</v>
+      </c>
+      <c r="M68" t="n">
+        <v>25</v>
+      </c>
+      <c r="N68" t="n">
+        <v>24</v>
+      </c>
+      <c r="O68" t="n">
+        <v>25</v>
+      </c>
+      <c r="P68" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R68" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V68" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W68" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X68" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>4042.29</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI68"/>
+  <dimension ref="A1:BI69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -14000,6 +14000,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>20260928</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>27</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G69" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>24</v>
+      </c>
+      <c r="J69" t="n">
+        <v>25</v>
+      </c>
+      <c r="K69" t="n">
+        <v>24</v>
+      </c>
+      <c r="L69" t="n">
+        <v>25</v>
+      </c>
+      <c r="M69" t="n">
+        <v>25</v>
+      </c>
+      <c r="N69" t="n">
+        <v>24</v>
+      </c>
+      <c r="O69" t="n">
+        <v>25</v>
+      </c>
+      <c r="P69" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R69" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V69" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W69" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X69" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>4042.29</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI69"/>
+  <dimension ref="A1:BI70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -14189,6 +14189,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>20260929</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>27</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>24</v>
+      </c>
+      <c r="J70" t="n">
+        <v>25</v>
+      </c>
+      <c r="K70" t="n">
+        <v>24</v>
+      </c>
+      <c r="L70" t="n">
+        <v>25</v>
+      </c>
+      <c r="M70" t="n">
+        <v>25</v>
+      </c>
+      <c r="N70" t="n">
+        <v>24</v>
+      </c>
+      <c r="O70" t="n">
+        <v>25</v>
+      </c>
+      <c r="P70" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R70" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S70" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V70" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W70" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X70" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>4042.29</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI70"/>
+  <dimension ref="A1:BI71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -14378,6 +14378,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>20260930</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>27</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G71" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>24</v>
+      </c>
+      <c r="J71" t="n">
+        <v>25</v>
+      </c>
+      <c r="K71" t="n">
+        <v>24</v>
+      </c>
+      <c r="L71" t="n">
+        <v>25</v>
+      </c>
+      <c r="M71" t="n">
+        <v>25</v>
+      </c>
+      <c r="N71" t="n">
+        <v>24</v>
+      </c>
+      <c r="O71" t="n">
+        <v>25</v>
+      </c>
+      <c r="P71" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R71" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S71" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V71" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W71" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X71" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>4042.29</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI71" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI71"/>
+  <dimension ref="A1:BI72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -14567,6 +14567,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>20261001</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>28</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F72" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>24</v>
+      </c>
+      <c r="J72" t="n">
+        <v>25</v>
+      </c>
+      <c r="K72" t="n">
+        <v>24</v>
+      </c>
+      <c r="L72" t="n">
+        <v>25</v>
+      </c>
+      <c r="M72" t="n">
+        <v>25</v>
+      </c>
+      <c r="N72" t="n">
+        <v>24</v>
+      </c>
+      <c r="O72" t="n">
+        <v>25</v>
+      </c>
+      <c r="P72" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R72" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V72" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W72" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X72" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>4042.28</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI72" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI72"/>
+  <dimension ref="A1:BI73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -14756,6 +14756,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>20261002</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>28</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F73" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>24</v>
+      </c>
+      <c r="J73" t="n">
+        <v>25</v>
+      </c>
+      <c r="K73" t="n">
+        <v>24</v>
+      </c>
+      <c r="L73" t="n">
+        <v>25</v>
+      </c>
+      <c r="M73" t="n">
+        <v>25</v>
+      </c>
+      <c r="N73" t="n">
+        <v>24</v>
+      </c>
+      <c r="O73" t="n">
+        <v>25</v>
+      </c>
+      <c r="P73" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R73" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S73" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V73" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W73" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X73" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>4042.26</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>4270.91</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI73" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI73"/>
+  <dimension ref="A1:BI74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -14945,6 +14945,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>20261003</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>28</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F74" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>24</v>
+      </c>
+      <c r="J74" t="n">
+        <v>25</v>
+      </c>
+      <c r="K74" t="n">
+        <v>24</v>
+      </c>
+      <c r="L74" t="n">
+        <v>25</v>
+      </c>
+      <c r="M74" t="n">
+        <v>25</v>
+      </c>
+      <c r="N74" t="n">
+        <v>24</v>
+      </c>
+      <c r="O74" t="n">
+        <v>25</v>
+      </c>
+      <c r="P74" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R74" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S74" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V74" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W74" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X74" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>4042.24</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>4270.9</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI74"/>
+  <dimension ref="A1:BI75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -15134,6 +15134,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>20261004</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>28</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>24</v>
+      </c>
+      <c r="J75" t="n">
+        <v>25</v>
+      </c>
+      <c r="K75" t="n">
+        <v>24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>25</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24</v>
+      </c>
+      <c r="O75" t="n">
+        <v>25</v>
+      </c>
+      <c r="P75" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R75" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S75" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U75" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V75" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W75" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>4042.24</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>4270.9</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI75"/>
+  <dimension ref="A1:BI76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -15323,6 +15323,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>20261005</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>28</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F76" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G76" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>24</v>
+      </c>
+      <c r="J76" t="n">
+        <v>25</v>
+      </c>
+      <c r="K76" t="n">
+        <v>24</v>
+      </c>
+      <c r="L76" t="n">
+        <v>25</v>
+      </c>
+      <c r="M76" t="n">
+        <v>25</v>
+      </c>
+      <c r="N76" t="n">
+        <v>24</v>
+      </c>
+      <c r="O76" t="n">
+        <v>25</v>
+      </c>
+      <c r="P76" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R76" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S76" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V76" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W76" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X76" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>4042.24</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>4270.87</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI76"/>
+  <dimension ref="A1:BI77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -15512,6 +15512,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>20261006</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>28</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>24</v>
+      </c>
+      <c r="J77" t="n">
+        <v>25</v>
+      </c>
+      <c r="K77" t="n">
+        <v>24</v>
+      </c>
+      <c r="L77" t="n">
+        <v>25</v>
+      </c>
+      <c r="M77" t="n">
+        <v>25</v>
+      </c>
+      <c r="N77" t="n">
+        <v>24</v>
+      </c>
+      <c r="O77" t="n">
+        <v>25</v>
+      </c>
+      <c r="P77" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R77" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S77" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T77" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U77" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V77" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W77" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X77" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>4042.22</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>4270.83</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI77"/>
+  <dimension ref="A1:BI78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -15701,6 +15701,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>20261007</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>28</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>24</v>
+      </c>
+      <c r="J78" t="n">
+        <v>25</v>
+      </c>
+      <c r="K78" t="n">
+        <v>24</v>
+      </c>
+      <c r="L78" t="n">
+        <v>25</v>
+      </c>
+      <c r="M78" t="n">
+        <v>25</v>
+      </c>
+      <c r="N78" t="n">
+        <v>24</v>
+      </c>
+      <c r="O78" t="n">
+        <v>25</v>
+      </c>
+      <c r="P78" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R78" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S78" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U78" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V78" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W78" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X78" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>4042.22</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>4270.83</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI78"/>
+  <dimension ref="A1:BI79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -15890,6 +15890,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>20261008</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>29</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>24</v>
+      </c>
+      <c r="J79" t="n">
+        <v>25</v>
+      </c>
+      <c r="K79" t="n">
+        <v>24</v>
+      </c>
+      <c r="L79" t="n">
+        <v>25</v>
+      </c>
+      <c r="M79" t="n">
+        <v>25</v>
+      </c>
+      <c r="N79" t="n">
+        <v>24</v>
+      </c>
+      <c r="O79" t="n">
+        <v>25</v>
+      </c>
+      <c r="P79" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R79" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S79" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V79" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W79" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X79" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>4042.22</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>4270.83</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI79"/>
+  <dimension ref="A1:BI80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -16079,6 +16079,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>29</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>24</v>
+      </c>
+      <c r="J80" t="n">
+        <v>25</v>
+      </c>
+      <c r="K80" t="n">
+        <v>24</v>
+      </c>
+      <c r="L80" t="n">
+        <v>25</v>
+      </c>
+      <c r="M80" t="n">
+        <v>25</v>
+      </c>
+      <c r="N80" t="n">
+        <v>24</v>
+      </c>
+      <c r="O80" t="n">
+        <v>25</v>
+      </c>
+      <c r="P80" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R80" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S80" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V80" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W80" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X80" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>4042.21</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>4270.83</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI80"/>
+  <dimension ref="A1:BI81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -16268,6 +16268,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>20261010</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>29</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F81" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>24</v>
+      </c>
+      <c r="J81" t="n">
+        <v>25</v>
+      </c>
+      <c r="K81" t="n">
+        <v>24</v>
+      </c>
+      <c r="L81" t="n">
+        <v>25</v>
+      </c>
+      <c r="M81" t="n">
+        <v>25</v>
+      </c>
+      <c r="N81" t="n">
+        <v>24</v>
+      </c>
+      <c r="O81" t="n">
+        <v>25</v>
+      </c>
+      <c r="P81" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R81" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T81" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U81" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V81" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W81" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X81" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>4042.19</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>4270.8</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI81"/>
+  <dimension ref="A1:BI82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -16457,6 +16457,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>20261011</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>29</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G82" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>24</v>
+      </c>
+      <c r="J82" t="n">
+        <v>25</v>
+      </c>
+      <c r="K82" t="n">
+        <v>24</v>
+      </c>
+      <c r="L82" t="n">
+        <v>25</v>
+      </c>
+      <c r="M82" t="n">
+        <v>25</v>
+      </c>
+      <c r="N82" t="n">
+        <v>24</v>
+      </c>
+      <c r="O82" t="n">
+        <v>25</v>
+      </c>
+      <c r="P82" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R82" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U82" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V82" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W82" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X82" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>4042.18</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>4270.8</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI82"/>
+  <dimension ref="A1:BI83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -16646,6 +16646,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>20261012</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>29</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G83" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>24</v>
+      </c>
+      <c r="J83" t="n">
+        <v>25</v>
+      </c>
+      <c r="K83" t="n">
+        <v>24</v>
+      </c>
+      <c r="L83" t="n">
+        <v>25</v>
+      </c>
+      <c r="M83" t="n">
+        <v>25</v>
+      </c>
+      <c r="N83" t="n">
+        <v>24</v>
+      </c>
+      <c r="O83" t="n">
+        <v>25</v>
+      </c>
+      <c r="P83" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R83" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S83" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T83" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U83" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V83" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W83" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X83" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>4042.16</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>4270.77</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI83"/>
+  <dimension ref="A1:BI84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -16835,6 +16835,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>20261013</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>29</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G84" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>24</v>
+      </c>
+      <c r="J84" t="n">
+        <v>25</v>
+      </c>
+      <c r="K84" t="n">
+        <v>24</v>
+      </c>
+      <c r="L84" t="n">
+        <v>25</v>
+      </c>
+      <c r="M84" t="n">
+        <v>25</v>
+      </c>
+      <c r="N84" t="n">
+        <v>24</v>
+      </c>
+      <c r="O84" t="n">
+        <v>25</v>
+      </c>
+      <c r="P84" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R84" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S84" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V84" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W84" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X84" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>4042.15</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>4270.72</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI84"/>
+  <dimension ref="A1:BI85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -17024,6 +17024,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>20261014</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>29</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>24</v>
+      </c>
+      <c r="J85" t="n">
+        <v>25</v>
+      </c>
+      <c r="K85" t="n">
+        <v>24</v>
+      </c>
+      <c r="L85" t="n">
+        <v>25</v>
+      </c>
+      <c r="M85" t="n">
+        <v>25</v>
+      </c>
+      <c r="N85" t="n">
+        <v>24</v>
+      </c>
+      <c r="O85" t="n">
+        <v>25</v>
+      </c>
+      <c r="P85" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R85" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S85" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T85" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U85" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V85" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W85" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X85" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>4042.15</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>4270.72</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI85"/>
+  <dimension ref="A1:BI86"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -17213,6 +17213,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>20261015</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>30</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>24</v>
+      </c>
+      <c r="J86" t="n">
+        <v>25</v>
+      </c>
+      <c r="K86" t="n">
+        <v>24</v>
+      </c>
+      <c r="L86" t="n">
+        <v>25</v>
+      </c>
+      <c r="M86" t="n">
+        <v>25</v>
+      </c>
+      <c r="N86" t="n">
+        <v>24</v>
+      </c>
+      <c r="O86" t="n">
+        <v>25</v>
+      </c>
+      <c r="P86" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R86" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S86" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T86" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U86" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V86" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W86" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X86" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>4042.14</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>4270.72</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI86"/>
+  <dimension ref="A1:BI87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -17402,6 +17402,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>30</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G87" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>24</v>
+      </c>
+      <c r="J87" t="n">
+        <v>25</v>
+      </c>
+      <c r="K87" t="n">
+        <v>24</v>
+      </c>
+      <c r="L87" t="n">
+        <v>25</v>
+      </c>
+      <c r="M87" t="n">
+        <v>25</v>
+      </c>
+      <c r="N87" t="n">
+        <v>24</v>
+      </c>
+      <c r="O87" t="n">
+        <v>25</v>
+      </c>
+      <c r="P87" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R87" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S87" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T87" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U87" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V87" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W87" t="n">
+        <v>4306.8</v>
+      </c>
+      <c r="X87" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>4042.13</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>4270.72</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI87"/>
+  <dimension ref="A1:BI88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -17591,6 +17591,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>20261017</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>30</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F88" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G88" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>24</v>
+      </c>
+      <c r="J88" t="n">
+        <v>25</v>
+      </c>
+      <c r="K88" t="n">
+        <v>24</v>
+      </c>
+      <c r="L88" t="n">
+        <v>25</v>
+      </c>
+      <c r="M88" t="n">
+        <v>25</v>
+      </c>
+      <c r="N88" t="n">
+        <v>24</v>
+      </c>
+      <c r="O88" t="n">
+        <v>25</v>
+      </c>
+      <c r="P88" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R88" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S88" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T88" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U88" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V88" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W88" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X88" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>4042.11</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>4270.65</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI88" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI88"/>
+  <dimension ref="A1:BI89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -17780,6 +17780,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>20261018</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>30</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G89" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>24</v>
+      </c>
+      <c r="J89" t="n">
+        <v>25</v>
+      </c>
+      <c r="K89" t="n">
+        <v>24</v>
+      </c>
+      <c r="L89" t="n">
+        <v>25</v>
+      </c>
+      <c r="M89" t="n">
+        <v>25</v>
+      </c>
+      <c r="N89" t="n">
+        <v>24</v>
+      </c>
+      <c r="O89" t="n">
+        <v>25</v>
+      </c>
+      <c r="P89" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R89" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S89" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T89" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U89" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V89" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W89" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X89" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>4042.1</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>4270.65</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI89"/>
+  <dimension ref="A1:BI90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -17969,6 +17969,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>20261019</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>30</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F90" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G90" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>24</v>
+      </c>
+      <c r="J90" t="n">
+        <v>25</v>
+      </c>
+      <c r="K90" t="n">
+        <v>24</v>
+      </c>
+      <c r="L90" t="n">
+        <v>25</v>
+      </c>
+      <c r="M90" t="n">
+        <v>25</v>
+      </c>
+      <c r="N90" t="n">
+        <v>24</v>
+      </c>
+      <c r="O90" t="n">
+        <v>25</v>
+      </c>
+      <c r="P90" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R90" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S90" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U90" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V90" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W90" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X90" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>4042.08</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>4270.65</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI90"/>
+  <dimension ref="A1:BI91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -18158,6 +18158,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>20261020</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>30</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F91" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G91" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>24</v>
+      </c>
+      <c r="J91" t="n">
+        <v>25</v>
+      </c>
+      <c r="K91" t="n">
+        <v>24</v>
+      </c>
+      <c r="L91" t="n">
+        <v>25</v>
+      </c>
+      <c r="M91" t="n">
+        <v>25</v>
+      </c>
+      <c r="N91" t="n">
+        <v>24</v>
+      </c>
+      <c r="O91" t="n">
+        <v>25</v>
+      </c>
+      <c r="P91" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R91" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S91" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T91" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U91" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V91" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W91" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X91" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>4042.07</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>4270.65</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI91" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI91"/>
+  <dimension ref="A1:BI92"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -18347,6 +18347,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>20261021</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>30</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G92" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D增辉</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>24</v>
+      </c>
+      <c r="J92" t="n">
+        <v>25</v>
+      </c>
+      <c r="K92" t="n">
+        <v>24</v>
+      </c>
+      <c r="L92" t="n">
+        <v>25</v>
+      </c>
+      <c r="M92" t="n">
+        <v>25</v>
+      </c>
+      <c r="N92" t="n">
+        <v>24</v>
+      </c>
+      <c r="O92" t="n">
+        <v>25</v>
+      </c>
+      <c r="P92" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R92" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S92" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T92" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U92" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V92" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W92" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X92" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>4042.06</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>4270.65</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI92" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI92"/>
+  <dimension ref="A1:BI93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -18536,6 +18536,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>20261022</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>31</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F93" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G93" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>24</v>
+      </c>
+      <c r="J93" t="n">
+        <v>25</v>
+      </c>
+      <c r="K93" t="n">
+        <v>24</v>
+      </c>
+      <c r="L93" t="n">
+        <v>25</v>
+      </c>
+      <c r="M93" t="n">
+        <v>25</v>
+      </c>
+      <c r="N93" t="n">
+        <v>24</v>
+      </c>
+      <c r="O93" t="n">
+        <v>25</v>
+      </c>
+      <c r="P93" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R93" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S93" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T93" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U93" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V93" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W93" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X93" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>4042.02</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>4270.61</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI93"/>
+  <dimension ref="A1:BI94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -18725,6 +18725,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>20261023</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>31</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F94" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>24</v>
+      </c>
+      <c r="J94" t="n">
+        <v>25</v>
+      </c>
+      <c r="K94" t="n">
+        <v>24</v>
+      </c>
+      <c r="L94" t="n">
+        <v>25</v>
+      </c>
+      <c r="M94" t="n">
+        <v>25</v>
+      </c>
+      <c r="N94" t="n">
+        <v>24</v>
+      </c>
+      <c r="O94" t="n">
+        <v>25</v>
+      </c>
+      <c r="P94" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R94" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S94" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T94" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U94" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V94" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W94" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X94" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>4042</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>4270.61</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI94"/>
+  <dimension ref="A1:BI95"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -18914,6 +18914,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>20261024</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>31</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>24</v>
+      </c>
+      <c r="J95" t="n">
+        <v>25</v>
+      </c>
+      <c r="K95" t="n">
+        <v>24</v>
+      </c>
+      <c r="L95" t="n">
+        <v>25</v>
+      </c>
+      <c r="M95" t="n">
+        <v>25</v>
+      </c>
+      <c r="N95" t="n">
+        <v>24</v>
+      </c>
+      <c r="O95" t="n">
+        <v>25</v>
+      </c>
+      <c r="P95" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R95" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S95" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T95" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U95" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V95" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W95" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X95" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>4041.98</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>4270.61</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI95" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI95"/>
+  <dimension ref="A1:BI96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -19103,6 +19103,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>20261025</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>31</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G96" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>24</v>
+      </c>
+      <c r="J96" t="n">
+        <v>25</v>
+      </c>
+      <c r="K96" t="n">
+        <v>24</v>
+      </c>
+      <c r="L96" t="n">
+        <v>25</v>
+      </c>
+      <c r="M96" t="n">
+        <v>25</v>
+      </c>
+      <c r="N96" t="n">
+        <v>24</v>
+      </c>
+      <c r="O96" t="n">
+        <v>25</v>
+      </c>
+      <c r="P96" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R96" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S96" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T96" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U96" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V96" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W96" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X96" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>4041.96</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>4270.61</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI96"/>
+  <dimension ref="A1:BI97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -19292,6 +19292,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>20261026</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>31</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F97" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G97" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>24</v>
+      </c>
+      <c r="J97" t="n">
+        <v>25</v>
+      </c>
+      <c r="K97" t="n">
+        <v>24</v>
+      </c>
+      <c r="L97" t="n">
+        <v>25</v>
+      </c>
+      <c r="M97" t="n">
+        <v>25</v>
+      </c>
+      <c r="N97" t="n">
+        <v>24</v>
+      </c>
+      <c r="O97" t="n">
+        <v>25</v>
+      </c>
+      <c r="P97" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R97" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S97" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T97" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U97" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V97" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W97" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X97" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>4041.96</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>4270.56</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI97"/>
+  <dimension ref="A1:BI98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -19481,6 +19481,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>20261027</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>31</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>24</v>
+      </c>
+      <c r="J98" t="n">
+        <v>25</v>
+      </c>
+      <c r="K98" t="n">
+        <v>24</v>
+      </c>
+      <c r="L98" t="n">
+        <v>25</v>
+      </c>
+      <c r="M98" t="n">
+        <v>25</v>
+      </c>
+      <c r="N98" t="n">
+        <v>24</v>
+      </c>
+      <c r="O98" t="n">
+        <v>25</v>
+      </c>
+      <c r="P98" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R98" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S98" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T98" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U98" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V98" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W98" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X98" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>4041.95</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>4270.54</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI98" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI98"/>
+  <dimension ref="A1:BI99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -19670,6 +19670,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>20261028</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>31</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G99" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>24</v>
+      </c>
+      <c r="J99" t="n">
+        <v>25</v>
+      </c>
+      <c r="K99" t="n">
+        <v>24</v>
+      </c>
+      <c r="L99" t="n">
+        <v>25</v>
+      </c>
+      <c r="M99" t="n">
+        <v>25</v>
+      </c>
+      <c r="N99" t="n">
+        <v>24</v>
+      </c>
+      <c r="O99" t="n">
+        <v>25</v>
+      </c>
+      <c r="P99" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R99" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S99" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T99" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U99" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V99" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W99" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X99" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>4041.93</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>4270.52</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI99"/>
+  <dimension ref="A1:BI100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -19859,6 +19859,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>20261029</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>32</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F100" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>24</v>
+      </c>
+      <c r="J100" t="n">
+        <v>25</v>
+      </c>
+      <c r="K100" t="n">
+        <v>24</v>
+      </c>
+      <c r="L100" t="n">
+        <v>25</v>
+      </c>
+      <c r="M100" t="n">
+        <v>25</v>
+      </c>
+      <c r="N100" t="n">
+        <v>24</v>
+      </c>
+      <c r="O100" t="n">
+        <v>25</v>
+      </c>
+      <c r="P100" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R100" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S100" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T100" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U100" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V100" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W100" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X100" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>4254.2</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>4041.92</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>4270.52</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI100" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI100"/>
+  <dimension ref="A1:BI101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -20048,6 +20048,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>20261030</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>32</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G101" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>24</v>
+      </c>
+      <c r="J101" t="n">
+        <v>25</v>
+      </c>
+      <c r="K101" t="n">
+        <v>24</v>
+      </c>
+      <c r="L101" t="n">
+        <v>25</v>
+      </c>
+      <c r="M101" t="n">
+        <v>25</v>
+      </c>
+      <c r="N101" t="n">
+        <v>24</v>
+      </c>
+      <c r="O101" t="n">
+        <v>25</v>
+      </c>
+      <c r="P101" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R101" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S101" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T101" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U101" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V101" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W101" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X101" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>4239</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>4041.92</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>4270.48</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/大秘境分数行情.xlsx
+++ b/大秘境分数行情.xlsx
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI101"/>
+  <dimension ref="A1:BI102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333333333333" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" style="2" min="1" max="1"/>
@@ -20237,6 +20237,195 @@
         <v>17079</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>20261031</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>至暗之夜S1</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>32</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4268.21</v>
+      </c>
+      <c r="G102" t="n">
+        <v>4035.99</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Speedk-D邪DK,Voluxar-D浩劫,Roibendeux-H奶僧,Sjelelele-D湮灭</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>24</v>
+      </c>
+      <c r="J102" t="n">
+        <v>25</v>
+      </c>
+      <c r="K102" t="n">
+        <v>24</v>
+      </c>
+      <c r="L102" t="n">
+        <v>25</v>
+      </c>
+      <c r="M102" t="n">
+        <v>25</v>
+      </c>
+      <c r="N102" t="n">
+        <v>24</v>
+      </c>
+      <c r="O102" t="n">
+        <v>25</v>
+      </c>
+      <c r="P102" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>4216.7</v>
+      </c>
+      <c r="R102" t="n">
+        <v>4268.2</v>
+      </c>
+      <c r="S102" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="T102" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="U102" t="n">
+        <v>4323.7</v>
+      </c>
+      <c r="V102" t="n">
+        <v>4299.9</v>
+      </c>
+      <c r="W102" t="n">
+        <v>4266.3</v>
+      </c>
+      <c r="X102" t="n">
+        <v>4379</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>4460.2</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>4137.5</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>4102.2</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>4295.7</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>4239</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>4278.3</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>4225.6</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>4376.8</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>4461.4</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>4307.3</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>4291.9</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>4217.3</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>4372.2</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>4379.7</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>4190.7</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>4369.3</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>4350.5</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>4342.5</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>4366.5</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>4379</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>4145.8</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>4361.3</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>4327.8</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>4340.4</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>4269</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>4041.9</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>4270.45</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>1707667</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>1708</v>
+      </c>
+      <c r="BI102" t="n">
+        <v>17079</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
